--- a/htr-strucGenerale-CDA/ig/StructureDefinition-StructureConservation.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-StructureConservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="96">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T10:35:11+00:00</t>
+    <t>2025-04-18T14:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -234,10 +234,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>*</t>
+    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -247,110 +244,37 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>StructureConservation.structure</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
+    <t xml:space="preserve">Base
 </t>
   </si>
   <si>
     <t>Structure</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>StructureConservation.structure.identifiantStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>StructureConservation.structure.id</t>
+    <t>Identifiant de la structure</t>
+  </si>
+  <si>
+    <t>StructureConservation.structure.nomStructure</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>StructureConservation.structure.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>StructureConservation.structure.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>StructureConservation.structure.identifiantStructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifiant de la structure</t>
-  </si>
-  <si>
-    <t>StructureConservation.structure.nomStructure</t>
   </si>
   <si>
     <t>Nom de la structure</t>
@@ -685,24 +609,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -716,7 +640,7 @@
     <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="43.625" customWidth="true" bestFit="true" hidden="true"/>
@@ -851,19 +775,19 @@
         <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -920,13 +844,13 @@
         <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AG2" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AH2" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>72</v>
@@ -937,10 +861,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -948,10 +872,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>72</v>
@@ -1020,27 +944,27 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH3" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AH3" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI3" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1048,11 +972,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
       </c>
@@ -1063,13 +987,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1120,13 +1044,13 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH4" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1137,22 +1061,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
       </c>
@@ -1163,17 +1087,15 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>72</v>
@@ -1210,75 +1132,71 @@
         <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH5" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AH5" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>72</v>
       </c>
@@ -1326,27 +1244,27 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1354,10 +1272,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1369,13 +1287,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1426,13 +1344,13 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>72</v>
@@ -1443,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1454,11 +1372,11 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
       </c>
@@ -1469,13 +1387,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1526,318 +1444,18 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AH8" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/htr-strucGenerale-CDA/ig/StructureDefinition-StructureConservation.xlsx
+++ b/htr-strucGenerale-CDA/ig/StructureDefinition-StructureConservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T14:53:38+00:00</t>
+    <t>2025-04-22T14:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -280,6 +280,16 @@
     <t>Nom de la structure</t>
   </si>
   <si>
+    <t>StructureConservation.structure.coordonneesTelecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
+</t>
+  </si>
+  <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>StructureConservation.structure.adresse</t>
   </si>
   <si>
@@ -288,26 +298,6 @@
   </si>
   <si>
     <t>Adresse géopostale</t>
-  </si>
-  <si>
-    <t>StructureConservation.structure.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>Coordonnées télécom</t>
-  </si>
-  <si>
-    <t>StructureConservation.structure.secteurActivite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Secteur d'activité</t>
   </si>
 </sst>
 </file>
@@ -609,7 +599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.625" customWidth="true" bestFit="true"/>
@@ -622,7 +612,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="10.96875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -872,7 +862,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>73</v>
@@ -947,7 +937,7 @@
         <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>73</v>
@@ -972,7 +962,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>73</v>
@@ -1047,7 +1037,7 @@
         <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>73</v>
@@ -1175,7 +1165,7 @@
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1250,7 +1240,7 @@
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>72</v>
@@ -1275,7 +1265,7 @@
         <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1350,112 +1340,12 @@
         <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
         <v>72</v>
       </c>
     </row>
